--- a/Config/Excel/Cards.xlsx
+++ b/Config/Excel/Cards.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500"/>
+    <workbookView windowWidth="23040" windowHeight="10500" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="卡牌" sheetId="1" r:id="rId1"/>
-    <sheet name="卡牌效果" sheetId="2" r:id="rId2"/>
-    <sheet name="枚举" sheetId="3" r:id="rId3"/>
+    <sheet name="Cards" sheetId="1" r:id="rId1"/>
+    <sheet name="Effects" sheetId="2" r:id="rId2"/>
+    <sheet name="Enums(参考)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="171">
   <si>
     <t>CardId</t>
   </si>
@@ -64,7 +64,7 @@
     <t>打击</t>
   </si>
   <si>
-    <t>对一名敌人造成6点伤害</t>
+    <t>造成6点伤害</t>
   </si>
   <si>
     <t>定策牌</t>
@@ -82,223 +82,262 @@
     <t>1001-1</t>
   </si>
   <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>获得5点护甲</t>
+  </si>
+  <si>
+    <t>自身</t>
+  </si>
+  <si>
+    <t>1002-1|1002-2</t>
+  </si>
+  <si>
     <t>铁斩波</t>
   </si>
   <si>
-    <t>获得4护甲并造成5点伤害</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>1002-1|1002-2</t>
-  </si>
-  <si>
-    <t>魔法盾</t>
-  </si>
-  <si>
-    <t>反制对手下回合首张伤害牌</t>
+    <t>获得4护甲并造成4点伤害</t>
+  </si>
+  <si>
+    <t>伤害|防御</t>
+  </si>
+  <si>
+    <t>1003-1|1003-2</t>
+  </si>
+  <si>
+    <t>暗影吞噬</t>
+  </si>
+  <si>
+    <t>造成6点伤害并恢复30%生命</t>
+  </si>
+  <si>
+    <t>1004-1|1004-2</t>
+  </si>
+  <si>
+    <t>治愈之光</t>
+  </si>
+  <si>
+    <t>恢复5点生命值</t>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
+    <t>1005-1</t>
+  </si>
+  <si>
+    <t>铁壁</t>
+  </si>
+  <si>
+    <t>获得8点护甲</t>
+  </si>
+  <si>
+    <t>1006-1</t>
+  </si>
+  <si>
+    <t>力量灌注</t>
+  </si>
+  <si>
+    <t>增加3点力量</t>
+  </si>
+  <si>
+    <t>增益</t>
+  </si>
+  <si>
+    <t>1007-1</t>
+  </si>
+  <si>
+    <t>弱化诅咒</t>
+  </si>
+  <si>
+    <t>使敌人易伤2回合</t>
+  </si>
+  <si>
+    <t>减益</t>
+  </si>
+  <si>
+    <t>1008-1</t>
+  </si>
+  <si>
+    <t>荆棘甲</t>
+  </si>
+  <si>
+    <t>获得4护甲并附带反伤效果</t>
+  </si>
+  <si>
+    <t>1009-1|1009-2</t>
+  </si>
+  <si>
+    <t>致命打击</t>
+  </si>
+  <si>
+    <t>造成12点伤害(斩杀型)</t>
+  </si>
+  <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>1010-1</t>
+  </si>
+  <si>
+    <t>EffectId</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>TargetOverride</t>
+  </si>
+  <si>
+    <t>TriggerCondition</t>
+  </si>
+  <si>
+    <t>IsDelayed</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1002-1</t>
+  </si>
+  <si>
+    <t>获得护甲</t>
+  </si>
+  <si>
+    <t>1002-2</t>
+  </si>
+  <si>
+    <t>1003-1</t>
+  </si>
+  <si>
+    <t>反制首张伤害牌</t>
+  </si>
+  <si>
+    <t>1004-1</t>
+  </si>
+  <si>
+    <t>1004-2</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>回复生命</t>
+  </si>
+  <si>
+    <t>增加力量</t>
+  </si>
+  <si>
+    <t>易伤</t>
+  </si>
+  <si>
+    <t>1009-1</t>
+  </si>
+  <si>
+    <t>1009-2</t>
+  </si>
+  <si>
+    <t>反伤</t>
+  </si>
+  <si>
+    <t>=== CardTrackType（双轨类型）===</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>瞬策牌</t>
+  </si>
+  <si>
+    <t>操作期即时生效</t>
+  </si>
+  <si>
+    <t>锁定期后统一结算</t>
+  </si>
+  <si>
+    <t>=== CardSubType（卡牌子类型 - Flags枚举，可组合）===</t>
+  </si>
+  <si>
+    <t>结算层</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>堆叠2层</t>
+  </si>
+  <si>
+    <t>可被反制</t>
+  </si>
+  <si>
+    <t>堆叠1层</t>
+  </si>
+  <si>
+    <t>护甲/护盾</t>
   </si>
   <si>
     <t>反制</t>
   </si>
   <si>
-    <t>1003-1</t>
-  </si>
-  <si>
-    <t>暗影吞噬</t>
-  </si>
-  <si>
-    <t>造成6点伤害并恢复30%生命</t>
-  </si>
-  <si>
-    <t>1004-1|1004-2</t>
-  </si>
-  <si>
-    <t>治愈之光</t>
-  </si>
-  <si>
-    <t>恢复5点生命值</t>
-  </si>
-  <si>
-    <t>资源</t>
-  </si>
-  <si>
-    <t>自身</t>
-  </si>
-  <si>
-    <t>1005-1</t>
-  </si>
-  <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>获得8点护甲</t>
-  </si>
-  <si>
-    <t>1006-1</t>
-  </si>
-  <si>
-    <t>力量灌注</t>
-  </si>
-  <si>
-    <t>增加3点力量</t>
-  </si>
-  <si>
-    <t>增益</t>
-  </si>
-  <si>
-    <t>1007-1</t>
-  </si>
-  <si>
-    <t>弱化诅咒</t>
-  </si>
-  <si>
-    <t>使敌人易伤2回合</t>
-  </si>
-  <si>
-    <t>减益</t>
-  </si>
-  <si>
-    <t>1008-1</t>
-  </si>
-  <si>
-    <t>荆棘甲</t>
-  </si>
-  <si>
-    <t>获得4护甲并附带反伤效果</t>
-  </si>
-  <si>
-    <t>1009-1|1009-2</t>
-  </si>
-  <si>
-    <t>致命打击</t>
-  </si>
-  <si>
-    <t>造成12点伤害(斩杀型)</t>
-  </si>
-  <si>
-    <t>斩杀</t>
-  </si>
-  <si>
-    <t>1010-1</t>
-  </si>
-  <si>
-    <t>EffectId</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>TargetOverride</t>
-  </si>
-  <si>
-    <t>TriggerCondition</t>
-  </si>
-  <si>
-    <t>IsDelayed</t>
-  </si>
-  <si>
-    <t>造成伤害</t>
-  </si>
-  <si>
-    <t>1002-1</t>
-  </si>
-  <si>
-    <t>获得护甲</t>
-  </si>
-  <si>
-    <t>1002-2</t>
-  </si>
-  <si>
-    <t>反制首张伤害牌</t>
-  </si>
-  <si>
-    <t>1004-1</t>
-  </si>
-  <si>
-    <t>1004-2</t>
-  </si>
-  <si>
-    <t>吸血</t>
-  </si>
-  <si>
-    <t>回复生命</t>
-  </si>
-  <si>
-    <t>增加力量</t>
-  </si>
-  <si>
-    <t>易伤</t>
-  </si>
-  <si>
-    <t>1009-1</t>
-  </si>
-  <si>
-    <t>1009-2</t>
-  </si>
-  <si>
-    <t>反伤</t>
-  </si>
-  <si>
-    <t>=== CardTrackType（双轨类型）===</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>瞬策牌</t>
-  </si>
-  <si>
-    <t>操作期即时生效</t>
-  </si>
-  <si>
-    <t>锁定期后统一结算</t>
-  </si>
-  <si>
-    <t>=== CardSubType（卡牌子类型）===</t>
-  </si>
-  <si>
-    <t>结算层</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>堆叠2层</t>
-  </si>
-  <si>
-    <t>堆叠1层</t>
-  </si>
-  <si>
     <t>堆叠0层</t>
   </si>
   <si>
+    <t>本回合锁定下回合触发</t>
+  </si>
+  <si>
     <t>堆叠1层/3层</t>
   </si>
   <si>
+    <t>正面buff</t>
+  </si>
+  <si>
+    <t>负面debuff</t>
+  </si>
+  <si>
     <t>支援</t>
   </si>
   <si>
     <t>堆叠3层</t>
   </si>
   <si>
+    <t>跨路支援</t>
+  </si>
+  <si>
     <t>传说特殊</t>
   </si>
   <si>
+    <t>传说专属</t>
+  </si>
+  <si>
     <t>控制</t>
+  </si>
+  <si>
+    <t>沉默/眩晕</t>
+  </si>
+  <si>
+    <t>抽牌/回能/回血</t>
+  </si>
+  <si>
+    <t>组合示例：伤害|防御 = 1+2 = 3（铁斩波：既是伤害又是防御）</t>
   </si>
   <si>
     <t>=== CardTargetType（目标类型）===</t>
@@ -515,7 +554,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,6 +567,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -976,161 +1022,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1186,7 +1225,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1196,9 +1235,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1206,39 +1245,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1270,7 +1309,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1305,135 +1343,171 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1446,373 +1520,371 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="10" style="2"/>
-    <col min="3" max="3" width="25.8888888888889" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.5555555555556" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.6666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.5555555555556" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.1111111111111" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="10" style="2"/>
+    <col min="2" max="2" width="16.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="32.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="19.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="12.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="14.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="17.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:10">
-      <c r="A2" s="2">
+    <row r="2" spans="1:10">
+      <c r="A2">
         <v>1001</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:10">
-      <c r="A3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2">
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
         <v>3</v>
       </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:10">
-      <c r="A4" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
-      <c r="A5" s="2">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3</v>
-      </c>
-      <c r="I5" s="2">
-        <v>3</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
-      <c r="A6" s="2">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
-      <c r="A7" s="2">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
-      <c r="A8" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:10">
-      <c r="A9" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:10">
-      <c r="A10" s="2">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:10">
-      <c r="A11" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="J11" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="2">
-        <v>4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1821,306 +1893,378 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="16384" width="10" style="2"/>
+    <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>1001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>1002</v>
+      </c>
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1001</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="2">
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5">
+        <v>1003</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6">
+        <v>1004</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>1005</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9">
+        <v>1006</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="b">
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10">
+        <v>1007</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11">
+        <v>1008</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12">
+        <v>1009</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E12">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="2" t="b">
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1002</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="2">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="G13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="b">
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1003</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1004</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="2">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1004</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="2">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1005</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="2">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1006</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="2">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:8">
-      <c r="A10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1007</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1008</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="2">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="H11" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="A12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1009</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1009</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="2">
-        <v>50</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1010</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="2">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -2128,40 +2272,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2169,26 +2313,29 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:3">
+        <v>81</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2196,10 +2343,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:3">
+        <v>82</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -2207,669 +2357,700 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:3">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:3">
+        <v>86</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:3">
+        <v>89</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:3">
+        <v>91</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:3">
+        <v>91</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B14" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B15" s="1">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B16" s="1">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="1">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:4">
+      <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="C22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="1">
         <v>0</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="C23" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:3">
-      <c r="A23" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:4">
+      <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B25" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="C25" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="1">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:3">
-      <c r="A25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="C26" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="1">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:3">
-      <c r="A26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="1">
+      <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="1">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="1">
+      <c r="C28" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="1">
         <v>6</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:3">
-      <c r="A29" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:3">
-      <c r="A30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:4">
+      <c r="A32" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:3">
-      <c r="A31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:3">
-      <c r="A32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="B33" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="B34" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="B35" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B36" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B37" s="1">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="1">
+        <v>16</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:4">
-      <c r="A40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>75</v>
+        <v>125</v>
+      </c>
+      <c r="B39" s="1">
+        <v>32</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="1">
-        <v>101</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" s="1">
-        <v>102</v>
+        <v>74</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="B43" s="1">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B44" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="B45" s="1">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B46" s="1">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="B47" s="1">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="B49" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B50" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B51" s="1">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="B52" s="1">
-        <v>211</v>
+        <v>116</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B53" s="1">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="B54" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B56" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B57" s="1">
-        <v>301</v>
+        <v>214</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B58" s="1">
-        <v>302</v>
+        <v>215</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="B60" s="1">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B61" s="1">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B63" s="1">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B64" s="1">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="B65" s="1">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>62</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B66" s="1">
+        <v>401</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="1">
+        <v>402</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B68" s="1">
         <v>403</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>157</v>
+      <c r="C68" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Excel/Cards.xlsx
+++ b/Config/Excel/Cards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10500" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="186">
   <si>
     <t>CardId</t>
   </si>
@@ -43,9 +43,6 @@
     <t>TrackType</t>
   </si>
   <si>
-    <t>SubType</t>
-  </si>
-  <si>
     <t>TargetType</t>
   </si>
   <si>
@@ -61,91 +58,145 @@
     <t>EffectsRef</t>
   </si>
   <si>
-    <t>打击</t>
-  </si>
-  <si>
-    <t>造成6点伤害</t>
-  </si>
-  <si>
-    <t>定策牌</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>敌方当前对手</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>1001-1</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>获得5点护甲</t>
-  </si>
-  <si>
-    <t>自身</t>
-  </si>
-  <si>
-    <t>1002-1|1002-2</t>
+    <t>火球术</t>
+  </si>
+  <si>
+    <t>对敌人造成4点伤害</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>CurrentEnemy</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>E1001-1</t>
+  </si>
+  <si>
+    <t>雷霆一击</t>
+  </si>
+  <si>
+    <t>凝聚雷电造成7点伤害</t>
+  </si>
+  <si>
+    <t>E1002-1</t>
+  </si>
+  <si>
+    <t>快速格挡</t>
+  </si>
+  <si>
+    <t>获得3点护盾</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>E1003-1</t>
+  </si>
+  <si>
+    <t>蓄力斩</t>
+  </si>
+  <si>
+    <t>蓄力后造成8点伤害</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>E2001-1</t>
+  </si>
+  <si>
+    <t>铁壁</t>
+  </si>
+  <si>
+    <t>获得5点护盾</t>
+  </si>
+  <si>
+    <t>E2002-1</t>
+  </si>
+  <si>
+    <t>生命回复</t>
+  </si>
+  <si>
+    <t>恢复5点生命值</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>E2003-1</t>
+  </si>
+  <si>
+    <t>见招拆招</t>
+  </si>
+  <si>
+    <t>反制敌方下回合首张伤害牌</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>E2004-1</t>
   </si>
   <si>
     <t>铁斩波</t>
   </si>
   <si>
-    <t>获得4护甲并造成4点伤害</t>
-  </si>
-  <si>
-    <t>伤害|防御</t>
-  </si>
-  <si>
-    <t>1003-1|1003-2</t>
+    <t>获得4护甲并造成5点伤害</t>
+  </si>
+  <si>
+    <t>Damage|Defense</t>
+  </si>
+  <si>
+    <t>E2005-1|E2005-2</t>
+  </si>
+  <si>
+    <t>战意激昂</t>
+  </si>
+  <si>
+    <t>获得2点力量</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>E2006-1</t>
   </si>
   <si>
     <t>暗影吞噬</t>
   </si>
   <si>
-    <t>造成6点伤害并恢复30%生命</t>
-  </si>
-  <si>
-    <t>1004-1|1004-2</t>
-  </si>
-  <si>
-    <t>治愈之光</t>
-  </si>
-  <si>
-    <t>恢复5点生命值</t>
-  </si>
-  <si>
-    <t>资源</t>
-  </si>
-  <si>
-    <t>1005-1</t>
-  </si>
-  <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>获得8点护甲</t>
-  </si>
-  <si>
-    <t>1006-1</t>
-  </si>
-  <si>
-    <t>力量灌注</t>
-  </si>
-  <si>
-    <t>增加3点力量</t>
-  </si>
-  <si>
-    <t>增益</t>
-  </si>
-  <si>
-    <t>1007-1</t>
+    <t>造成6点伤害并吸血30%</t>
+  </si>
+  <si>
+    <t>E2007-1|E2007-2</t>
+  </si>
+  <si>
+    <t>致命打击</t>
+  </si>
+  <si>
+    <t>造成12点伤害</t>
+  </si>
+  <si>
+    <t>Damage|Exhaust</t>
+  </si>
+  <si>
+    <t>E2008-1</t>
+  </si>
+  <si>
+    <t>荆棘甲</t>
+  </si>
+  <si>
+    <t>获得4护甲并附带反伤</t>
+  </si>
+  <si>
+    <t>E2009-1|E2009-2</t>
   </si>
   <si>
     <t>弱化诅咒</t>
@@ -154,31 +205,10 @@
     <t>使敌人易伤2回合</t>
   </si>
   <si>
-    <t>减益</t>
-  </si>
-  <si>
-    <t>1008-1</t>
-  </si>
-  <si>
-    <t>荆棘甲</t>
-  </si>
-  <si>
-    <t>获得4护甲并附带反伤效果</t>
-  </si>
-  <si>
-    <t>1009-1|1009-2</t>
-  </si>
-  <si>
-    <t>致命打击</t>
-  </si>
-  <si>
-    <t>造成12点伤害(斩杀型)</t>
-  </si>
-  <si>
-    <t>斩杀</t>
-  </si>
-  <si>
-    <t>1010-1</t>
+    <t>Debuff</t>
+  </si>
+  <si>
+    <t>E2010-1</t>
   </si>
   <si>
     <t>EffectId</t>
@@ -202,52 +232,52 @@
     <t>IsDelayed</t>
   </si>
   <si>
-    <t>造成伤害</t>
+    <t>DealDamage</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>1002-1</t>
-  </si>
-  <si>
-    <t>获得护甲</t>
-  </si>
-  <si>
-    <t>1002-2</t>
-  </si>
-  <si>
-    <t>1003-1</t>
-  </si>
-  <si>
-    <t>反制首张伤害牌</t>
-  </si>
-  <si>
-    <t>1004-1</t>
-  </si>
-  <si>
-    <t>1004-2</t>
-  </si>
-  <si>
-    <t>吸血</t>
-  </si>
-  <si>
-    <t>回复生命</t>
-  </si>
-  <si>
-    <t>增加力量</t>
-  </si>
-  <si>
-    <t>易伤</t>
-  </si>
-  <si>
-    <t>1009-1</t>
-  </si>
-  <si>
-    <t>1009-2</t>
-  </si>
-  <si>
-    <t>反伤</t>
+    <t>GainShield</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>CounterFirstDamage</t>
+  </si>
+  <si>
+    <t>E2005-1</t>
+  </si>
+  <si>
+    <t>GainArmor</t>
+  </si>
+  <si>
+    <t>E2005-2</t>
+  </si>
+  <si>
+    <t>GainStrength</t>
+  </si>
+  <si>
+    <t>E2007-1</t>
+  </si>
+  <si>
+    <t>E2007-2</t>
+  </si>
+  <si>
+    <t>Lifesteal</t>
+  </si>
+  <si>
+    <t>E2009-1</t>
+  </si>
+  <si>
+    <t>E2009-2</t>
+  </si>
+  <si>
+    <t>Thorns</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
   </si>
   <si>
     <t>=== CardTrackType（双轨类型）===</t>
@@ -262,286 +292,301 @@
     <t>说明</t>
   </si>
   <si>
-    <t>瞬策牌</t>
-  </si>
-  <si>
-    <t>操作期即时生效</t>
-  </si>
-  <si>
-    <t>锁定期后统一结算</t>
-  </si>
-  <si>
-    <t>=== CardSubType（卡牌子类型 - Flags枚举，可组合）===</t>
+    <t>瞬策牌：操作期即时生效</t>
+  </si>
+  <si>
+    <t>定策牌：锁定期后统一结算</t>
+  </si>
+  <si>
+    <t>=== CardTargetType（目标类型）===</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无目标：无需选择目标</t>
+  </si>
+  <si>
+    <t>自身：作用于自己</t>
+  </si>
+  <si>
+    <t>敌方当前对手：对线对手（自动选择）</t>
+  </si>
+  <si>
+    <t>AnyEnemy</t>
+  </si>
+  <si>
+    <t>敌方任意：可选择敌方任意玩家</t>
+  </si>
+  <si>
+    <t>AnyAlly</t>
+  </si>
+  <si>
+    <t>友方任意：可选择友方任意玩家</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>全体敌方：AOE敌方</t>
+  </si>
+  <si>
+    <t>AllAllies</t>
+  </si>
+  <si>
+    <t>全体友方：AOE友方</t>
+  </si>
+  <si>
+    <t>=== CardTag（卡牌标签 - Flags枚举，可组合）===</t>
+  </si>
+  <si>
+    <t>默认无标签</t>
+  </si>
+  <si>
+    <t>--- 用途分类 ---</t>
+  </si>
+  <si>
+    <t>伤害型：可被反制牌针对</t>
+  </si>
+  <si>
+    <t>防御型：护甲/护盾相关</t>
+  </si>
+  <si>
+    <t>反制型：本回合暗置下回合触发</t>
+  </si>
+  <si>
+    <t>增益型：正面buff效果</t>
+  </si>
+  <si>
+    <t>减益型：负面debuff效果</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>支援型：跨路支援相关</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>传说型：传说卡专属（使用后消耗）</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>控制型：沉默/眩晕效果</t>
+  </si>
+  <si>
+    <t>资源型：抽牌/回能/回血</t>
+  </si>
+  <si>
+    <t>--- 行为标签 ---</t>
+  </si>
+  <si>
+    <t>CrossLane</t>
+  </si>
+  <si>
+    <t>跨路生效：可对其他路敌人生效</t>
+  </si>
+  <si>
+    <t>Recycle</t>
+  </si>
+  <si>
+    <t>卡组循环：使用后返回牌库底部</t>
+  </si>
+  <si>
+    <t>Exhaust</t>
+  </si>
+  <si>
+    <t>消耗：使用后移出游戏（不进弃牌堆）</t>
+  </si>
+  <si>
+    <t>SilentPlay</t>
+  </si>
+  <si>
+    <t>静默出牌：不触发出牌时效果</t>
+  </si>
+  <si>
+    <t>Unblockable</t>
+  </si>
+  <si>
+    <t>无法格挡：无视护盾直接扣血</t>
+  </si>
+  <si>
+    <t>组合示例：</t>
+  </si>
+  <si>
+    <t>- Damage|Defense = 1+2 = 3（铁斩波：既造成伤害又提供护甲）</t>
+  </si>
+  <si>
+    <t>- Damage|Exhaust = 1+2048 = 2049（终极爆发：高伤害但使用后消耗）</t>
+  </si>
+  <si>
+    <t>- Counter|CrossLane = 4+512 = 516（跨路反制：可反制其他路的伤害牌）</t>
+  </si>
+  <si>
+    <t>=== EffectType（效果类型 - 决定结算顺序）===</t>
   </si>
   <si>
     <t>结算层</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>堆叠2层</t>
-  </si>
-  <si>
-    <t>可被反制</t>
+    <t>--- 堆叠0层：反制效果（最先执行）---</t>
+  </si>
+  <si>
+    <t>CounterCard</t>
+  </si>
+  <si>
+    <t>堆叠0层</t>
+  </si>
+  <si>
+    <t>反制卡牌：使目标卡牌无效</t>
+  </si>
+  <si>
+    <t>反制首张伤害牌：无效化敌方首张伤害牌</t>
+  </si>
+  <si>
+    <t>CounterAndReflect</t>
+  </si>
+  <si>
+    <t>反制并反弹：使目标卡牌无效并反弹效果</t>
+  </si>
+  <si>
+    <t>--- 堆叠1层：防御/属性效果 ---</t>
   </si>
   <si>
     <t>堆叠1层</t>
   </si>
   <si>
-    <t>护甲/护盾</t>
-  </si>
-  <si>
-    <t>反制</t>
-  </si>
-  <si>
-    <t>堆叠0层</t>
-  </si>
-  <si>
-    <t>本回合锁定下回合触发</t>
-  </si>
-  <si>
-    <t>堆叠1层/3层</t>
-  </si>
-  <si>
-    <t>正面buff</t>
-  </si>
-  <si>
-    <t>负面debuff</t>
-  </si>
-  <si>
-    <t>支援</t>
+    <t>获得护甲：减少受到的伤害</t>
+  </si>
+  <si>
+    <t>获得护盾：吸收伤害</t>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+  </si>
+  <si>
+    <t>伤害减免：百分比减少受到的伤害</t>
+  </si>
+  <si>
+    <t>Invincible</t>
+  </si>
+  <si>
+    <t>无敌：完全免疫伤害</t>
+  </si>
+  <si>
+    <t>增加力量：增加造成的伤害</t>
+  </si>
+  <si>
+    <t>ReduceStrength</t>
+  </si>
+  <si>
+    <t>降低力量：减少造成的伤害</t>
+  </si>
+  <si>
+    <t>BreakArmor</t>
+  </si>
+  <si>
+    <t>破甲：降低目标护甲</t>
+  </si>
+  <si>
+    <t>Penetrate</t>
+  </si>
+  <si>
+    <t>穿透：无视目标护甲</t>
+  </si>
+  <si>
+    <t>易伤：目标受到的伤害增加</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>虚弱：目标造成的伤害减少</t>
+  </si>
+  <si>
+    <t>--- 堆叠2层：伤害效果 ---</t>
+  </si>
+  <si>
+    <t>堆叠2层-步骤1</t>
+  </si>
+  <si>
+    <t>造成伤害：直接扣减目标生命值</t>
+  </si>
+  <si>
+    <t>堆叠2层-步骤2</t>
+  </si>
+  <si>
+    <t>反伤：受到伤害时反弹伤害</t>
+  </si>
+  <si>
+    <t>吸血：造成伤害时回复生命</t>
+  </si>
+  <si>
+    <t>HealOnHit</t>
+  </si>
+  <si>
+    <t>受击回血：受到伤害时回复生命</t>
+  </si>
+  <si>
+    <t>ArmorOnHit</t>
+  </si>
+  <si>
+    <t>受击获得护甲：受到伤害时获得护甲</t>
+  </si>
+  <si>
+    <t>HealOnKill</t>
+  </si>
+  <si>
+    <t>击杀回血：击杀敌人时回复生命</t>
+  </si>
+  <si>
+    <t>--- 堆叠3层：功能效果 ---</t>
+  </si>
+  <si>
+    <t>DrawCard</t>
   </si>
   <si>
     <t>堆叠3层</t>
   </si>
   <si>
-    <t>跨路支援</t>
-  </si>
-  <si>
-    <t>传说特殊</t>
-  </si>
-  <si>
-    <t>传说专属</t>
-  </si>
-  <si>
-    <t>控制</t>
-  </si>
-  <si>
-    <t>沉默/眩晕</t>
-  </si>
-  <si>
-    <t>抽牌/回能/回血</t>
-  </si>
-  <si>
-    <t>组合示例：伤害|防御 = 1+2 = 3（铁斩波：既是伤害又是防御）</t>
-  </si>
-  <si>
-    <t>=== CardTargetType（目标类型）===</t>
-  </si>
-  <si>
-    <t>无目标</t>
-  </si>
-  <si>
-    <t>无需选择目标</t>
-  </si>
-  <si>
-    <t>作用于自己</t>
-  </si>
-  <si>
-    <t>对线对手</t>
-  </si>
-  <si>
-    <t>敌方任意</t>
-  </si>
-  <si>
-    <t>可选择敌方任意玩家</t>
-  </si>
-  <si>
-    <t>友方任意</t>
-  </si>
-  <si>
-    <t>可选择友方任意玩家</t>
-  </si>
-  <si>
-    <t>全体敌方</t>
-  </si>
-  <si>
-    <t>AOE敌方</t>
-  </si>
-  <si>
-    <t>全体友方</t>
-  </si>
-  <si>
-    <t>AOE友方</t>
-  </si>
-  <si>
-    <t>=== CardTag（卡牌标签 - 可组合）===</t>
-  </si>
-  <si>
-    <t>无特殊标签</t>
-  </si>
-  <si>
-    <t>跨路生效</t>
-  </si>
-  <si>
-    <t>可对其他路敌人生效</t>
-  </si>
-  <si>
-    <t>卡组循环</t>
-  </si>
-  <si>
-    <t>使用后返回牌库</t>
-  </si>
-  <si>
-    <t>防御相关</t>
-  </si>
-  <si>
-    <t>控制相关</t>
-  </si>
-  <si>
-    <t>斩杀相关</t>
-  </si>
-  <si>
-    <t>消耗</t>
-  </si>
-  <si>
-    <t>使用后移出游戏</t>
-  </si>
-  <si>
-    <t>=== EffectType（效果类型）===</t>
-  </si>
-  <si>
-    <t>减少受到的伤害</t>
-  </si>
-  <si>
-    <t>获得护盾</t>
-  </si>
-  <si>
-    <t>吸收伤害</t>
-  </si>
-  <si>
-    <t>伤害减免</t>
-  </si>
-  <si>
-    <t>百分比减少受到的伤害</t>
-  </si>
-  <si>
-    <t>无敌</t>
-  </si>
-  <si>
-    <t>完全免疫伤害</t>
-  </si>
-  <si>
-    <t>增加造成的伤害</t>
-  </si>
-  <si>
-    <t>降低力量</t>
-  </si>
-  <si>
-    <t>减少造成的伤害</t>
-  </si>
-  <si>
-    <t>破甲</t>
-  </si>
-  <si>
-    <t>降低目标护甲</t>
-  </si>
-  <si>
-    <t>穿透</t>
-  </si>
-  <si>
-    <t>无视目标护甲</t>
-  </si>
-  <si>
-    <t>目标受到的伤害增加</t>
-  </si>
-  <si>
-    <t>虚弱</t>
-  </si>
-  <si>
-    <t>目标造成的伤害减少</t>
-  </si>
-  <si>
-    <t>堆叠2层-步骤1</t>
-  </si>
-  <si>
-    <t>直接扣减目标生命值</t>
-  </si>
-  <si>
-    <t>堆叠2层-步骤2</t>
-  </si>
-  <si>
-    <t>受到伤害时反弹伤害</t>
-  </si>
-  <si>
-    <t>造成伤害时回复生命</t>
-  </si>
-  <si>
-    <t>受击回血</t>
-  </si>
-  <si>
-    <t>受到伤害时回复生命</t>
-  </si>
-  <si>
-    <t>受击获得护甲</t>
-  </si>
-  <si>
-    <t>受到伤害时获得护甲</t>
-  </si>
-  <si>
-    <t>击杀回血</t>
-  </si>
-  <si>
-    <t>击杀敌人时回复生命</t>
-  </si>
-  <si>
-    <t>抽牌</t>
-  </si>
-  <si>
-    <t>从牌库抽取卡牌</t>
-  </si>
-  <si>
-    <t>弃牌</t>
-  </si>
-  <si>
-    <t>弃置手牌</t>
-  </si>
-  <si>
-    <t>回复能量</t>
-  </si>
-  <si>
-    <t>沉默</t>
-  </si>
-  <si>
-    <t>禁止使用技能牌</t>
-  </si>
-  <si>
-    <t>眩晕</t>
-  </si>
-  <si>
-    <t>跳过操作回合</t>
-  </si>
-  <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>行动顺序降低</t>
-  </si>
-  <si>
-    <t>反制卡牌</t>
-  </si>
-  <si>
-    <t>使目标卡牌无效</t>
-  </si>
-  <si>
-    <t>反制并反弹</t>
-  </si>
-  <si>
-    <t>使目标卡牌无效并反弹效果</t>
+    <t>抽牌：从牌库抽取卡牌</t>
+  </si>
+  <si>
+    <t>DiscardCard</t>
+  </si>
+  <si>
+    <t>弃牌：弃置手牌</t>
+  </si>
+  <si>
+    <t>RestoreEnergy</t>
+  </si>
+  <si>
+    <t>回复能量：回复能量</t>
+  </si>
+  <si>
+    <t>回复生命：回复生命</t>
+  </si>
+  <si>
+    <t>Silence</t>
+  </si>
+  <si>
+    <t>沉默：禁止使用技能牌</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>眩晕：跳过操作回合</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>减速：行动顺序降低</t>
   </si>
 </sst>
 </file>
@@ -1519,19 +1564,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="32.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="19.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="12.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="14.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="16.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="17.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="21.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="19.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1559,301 +1600,271 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>2001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>2002</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>2003</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>2004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8">
         <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>2005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9">
         <v>2</v>
-      </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>2006</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="J9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="I10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:9">
       <c r="A11">
-        <v>1010</v>
+        <v>2007</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
@@ -1862,25 +1873,109 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
         <v>48</v>
       </c>
-      <c r="H11">
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>2008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="I11">
+      <c r="H12">
         <v>3</v>
       </c>
-      <c r="J11" t="s">
-        <v>49</v>
+      <c r="I12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>2009</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>2010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1892,60 +1987,59 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="10.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="14.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="24.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1953,25 +2047,25 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -1979,25 +2073,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -2005,51 +2099,51 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>1004</v>
+        <v>2002</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -2057,25 +2151,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>1004</v>
+        <v>2003</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -2083,51 +2177,51 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B8">
-        <v>1005</v>
+        <v>2004</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B9">
-        <v>1006</v>
+        <v>2005</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -2135,25 +2229,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B10">
-        <v>1007</v>
+        <v>2005</v>
       </c>
       <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
         <v>68</v>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -2161,25 +2255,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B11">
-        <v>1008</v>
+        <v>2006</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -2187,25 +2281,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B12">
-        <v>1009</v>
+        <v>2007</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -2213,25 +2307,25 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B13">
-        <v>1009</v>
+        <v>2007</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -2239,13 +2333,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14">
-        <v>1010</v>
+        <v>2008</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D14">
         <v>12</v>
@@ -2254,12 +2348,90 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15">
+        <v>2009</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16">
+        <v>2009</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16">
+        <v>50</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17">
+        <v>2010</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2272,781 +2444,755 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="1">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1">
         <v>4</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1">
+      <c r="C23" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1">
         <v>8</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="C24" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1">
         <v>16</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="C25" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="1">
         <v>32</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="C26" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="1">
         <v>64</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="C27" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="1">
         <v>128</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="1">
+      <c r="C28" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="1">
         <v>256</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:4">
-      <c r="A22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:4">
-      <c r="A23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:4">
-      <c r="A24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:4">
-      <c r="A25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="1">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" s="1">
-        <v>6</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>75</v>
+        <v>118</v>
+      </c>
+      <c r="B32" s="1">
+        <v>512</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="B33" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>2048</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B35" s="1">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B36" s="1">
-        <v>4</v>
+        <v>8192</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:4">
-      <c r="A37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="1">
-        <v>8</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="1">
-        <v>16</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" s="1">
-        <v>32</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:4">
-      <c r="A42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="1">
-        <v>101</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="1">
-        <v>102</v>
+        <v>84</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:4">
-      <c r="A45" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" s="1">
-        <v>103</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B46" s="1">
-        <v>104</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="B47" s="1">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:4">
       <c r="A48" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="1">
-        <v>112</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B49" s="1">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:4">
-      <c r="A50" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B50" s="1">
-        <v>114</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51" s="1">
-        <v>115</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:4">
       <c r="A52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="1">
+        <v>101</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B52" s="1">
-        <v>116</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="B54" s="1">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="B55" s="1">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="B56" s="1">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B57" s="1">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B58" s="1">
-        <v>215</v>
+        <v>113</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B59" s="1">
-        <v>301</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="B60" s="1">
-        <v>302</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B61" s="1">
-        <v>303</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:4">
-      <c r="A62" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="1">
-        <v>304</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B63" s="1">
-        <v>311</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="B64" s="1">
-        <v>312</v>
+        <v>201</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="B65" s="1">
-        <v>313</v>
+        <v>211</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="B66" s="1">
-        <v>401</v>
+        <v>212</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:4">
       <c r="A67" s="1" t="s">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1">
-        <v>402</v>
+        <v>213</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:4">
       <c r="A68" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="1">
+        <v>214</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:4">
+      <c r="A69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B68" s="1">
-        <v>403</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="B69" s="1">
+        <v>215</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>170</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" s="1">
+        <v>301</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B73" s="1">
+        <v>302</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B74" s="1">
+        <v>303</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="1">
+        <v>304</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B76" s="1">
+        <v>311</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="1">
+        <v>312</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B78" s="1">
+        <v>313</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/Cards.xlsx
+++ b/Config/Excel/Cards.xlsx
@@ -599,7 +599,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,13 +612,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1068,148 +1061,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1568,8 +1561,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="21.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="26.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="19.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="15.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">

--- a/Config/Excel/Cards.xlsx
+++ b/Config/Excel/Cards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,12 +502,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>战斗专注</t>
+          <t>持盾向前</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>抽3张牌</t>
+          <t>抽 1 张牌，获得 4 点护盾。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,28 +532,28 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>DefenseModifier</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Defense|Resource</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Draw 3</t>
+          <t>Draw 1 -&gt;Self ; Shield 4 -&gt;Self</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[{"effectType":24,"value":3,"repeatCount":1,"duration":0}]</t>
+          <t>[{"effectType":24,"value":1,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":2,"value":4,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>突破极限</t>
+          <t>锻体</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>获得4点力量（消耗）</t>
+          <t>本回合内，获得 2 点力量。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -593,109 +593,109 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Utility</t>
+          <t>BuffSpecial</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Buff|Exhaust</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AddBuff 4 -&gt;Self buff=strength</t>
+          <t>AddBuff 2 -&gt;Self dur=1 buff=strength</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[{"effectType":31,"value":4,"repeatCount":1,"duration":0,"targetOverride":"Self","buffConfigId":"strength"}]</t>
+          <t>[{"effectType":31,"value":2,"repeatCount":1,"duration":1,"targetOverride":"Self","buffConfigId":"strength"}]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>打击</t>
+          <t>放血</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>造成6点伤害</t>
+          <t>你受到 3 点物理伤害，获得 2 点能量。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CurrentEnemy</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SingleEnemy</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DamageTrigger</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Damage 6</t>
+          <t>Damage 3 -&gt;Self ; GainEnergy 2 -&gt;Self</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[{"effectType":10,"value":6,"repeatCount":1,"duration":0}]</t>
+          <t>[{"effectType":10,"value":3,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":26,"value":2,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2002</v>
+        <v>1004</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>疲劳行军</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>获得5点护盾</t>
+          <t>抽 2 张牌，获得 1 层虚弱。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -715,12 +715,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DefenseModifier</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -731,32 +731,32 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Shield 5 -&gt;Self</t>
+          <t>Draw 2 -&gt;Self ; AddBuff 25 -&gt;Self dur=1 buff=weak</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[{"effectType":2,"value":5,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
+          <t>[{"effectType":24,"value":2,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":31,"value":25,"repeatCount":1,"duration":1,"targetOverride":"Self","buffConfigId":"weak"}]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2003</v>
+        <v>1005</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>观察弱点</t>
+          <t>竭泽而渔</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>若敌方本回合打出过伤害牌则获得2点力量</t>
+          <t>抽 3 张牌。本回合内，你不能再抽牌。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -776,43 +776,43 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BuffSpecial</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AddBuff 2 -&gt;Self buff=strength if[EnemyPlayedDamageCard]</t>
+          <t>Draw 3 -&gt;Self ; AddBuff 1 -&gt;Self dur=1 buff=no_draw_this_turn</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[{"effectType":31,"value":2,"repeatCount":1,"duration":0,"targetOverride":"Self","buffConfigId":"strength","effectConditions":[{"conditionType":"EnemyPlayedDamageCard","threshold":0,"negate":false,"conditionBuffType":""}]}]</t>
+          <t>[{"effectType":24,"value":3,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":31,"value":1,"repeatCount":1,"duration":1,"targetOverride":"Self","buffConfigId":"no_draw_this_turn"}]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>死亡收割</t>
+          <t>无情连打</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>对所有敌方造成3点伤害并按实际造成的生命伤害吸血</t>
+          <t>造成 3 点物理伤害 3 次。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AllEnemies</t>
+          <t>CurrentEnemy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AllEnemies</t>
+          <t>SingleEnemy</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -846,34 +846,34 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Damage 3 -&gt;AllEnemies ; Lifesteal 100 -&gt;Self</t>
+          <t>Damage 3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[{"effectType":10,"value":3,"repeatCount":1,"duration":0,"targetOverride":"AllEnemies"},{"effectType":11,"value":100,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
+          <t>[{"effectType":10,"value":3,"repeatCount":3,"duration":0}]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>飞剑回旋镖</t>
+          <t>以血还血</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>对当前敌人造成3点伤害4次</t>
+          <t>你受到 3 点物理伤害。造成 15 点物理伤害。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -914,12 +914,561 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Damage 3 x4</t>
+          <t>Damage 3 -&gt;Self ; Damage 15</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[{"effectType":10,"value":3,"repeatCount":4,"duration":0}]</t>
+          <t>[{"effectType":10,"value":3,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":10,"value":15,"repeatCount":1,"duration":0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>鲜血护盾</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>你受到 2 点物理伤害，获得 10 点护盾。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DefenseModifier</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Damage 2 -&gt;Self ; Shield 10 -&gt;Self</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":2,"repeatCount":1,"duration":0,"targetOverride":"Self"},{"effectType":2,"value":10,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>死亡收割</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>对所有敌人造成 3 点物理伤害。回复等同于其中未被格挡伤害总和的生命值。消耗。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AllEnemies</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AllEnemies</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Damage|Resource|Exhaust</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Damage 3 -&gt;AllEnemies ; Lifesteal 100 -&gt;Self</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":3,"repeatCount":1,"duration":0,"targetOverride":"AllEnemies"},{"effectType":11,"value":100,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>护盾猛击</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>造成 6 点物理伤害。结算时，你每有 1 点护盾，该伤害额外提高 1 点。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Damage {{6 + self.shield}}</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":0,"valueExpression":"{{6 + self.shield}}","repeatCount":1,"duration":0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>全力一击</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>造成 25 点物理伤害。下回合内，你不能再打出伤害牌。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Damage 25 ; AddBuff 1 -&gt;Self dur=2 buff=no_damage_card_this_turn</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":25,"repeatCount":1,"duration":0},{"effectType":31,"value":1,"repeatCount":1,"duration":2,"targetOverride":"Self","buffConfigId":"no_damage_card_this_turn"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>撕裂</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>造成 12 点物理伤害。若此伤害未被格挡，向目标的抽牌堆洗入 1 张伤口。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Damage|Debuff</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Damage 12 ; GenerateCard x1 card=3001@Deck</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":12,"repeatCount":1,"duration":0},{"effectType":32,"value":1,"valueExpression":"{{preEffect[fx_00].totalRealHpDamage}}","repeatCount":1,"duration":0,"generateCardConfigId":"3001","generateCardZone":"Deck","generateCardIsTemp":false}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>愤怒</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>造成 6 点物理伤害。将 1 张此牌的复制洗入你的抽牌堆。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Damage 6 ; GenerateCard x1 -&gt;Self card=2008@Deck</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":6,"repeatCount":1,"duration":0},{"effectType":32,"value":1,"repeatCount":1,"duration":0,"targetOverride":"Self","generateCardConfigId":"2008","generateCardZone":"Deck","generateCardIsTemp":false}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>回旋镖</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>造成 8 点物理伤害。回合结束时，若此牌位于你的弃牌堆中，将其返回手牌。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Damage|Resource</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Damage 8 ; return-source-card@end-round</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":8,"repeatCount":1,"duration":0},{"effectType":34,"value":1,"repeatCount":1,"duration":0,"targetOverride":"Self"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>痛击</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>造成 8 点物理伤害。下回合开始时，目标获得 1 层易伤。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CurrentEnemy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DamageTrigger</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Damage|Debuff</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Damage 8 ; AddBuff 50 -&gt;Enemy dur=2 buff=delayed_vulnerable_next_round</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[{"effectType":10,"value":8,"repeatCount":1,"duration":0},{"effectType":31,"value":50,"repeatCount":1,"duration":2,"targetOverride":"Enemy","buffConfigId":"delayed_vulnerable_next_round"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>伤口</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>状态牌。无法主动打出。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>BuffSpecial</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Debuff|Status</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>状态牌（无主动效果）</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
